--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/7714-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/7714-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80286AA4-A7DA-416E-BE2C-6A407EF94518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA4B2668-68A4-4AD5-8E7D-7BEEFA5437EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{A032EEBE-22B7-4216-A807-0ED1F8FEBA5C}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{D8B8A3CD-BB4B-4816-A38D-7304983ACEA1}"/>
   </bookViews>
   <sheets>
     <sheet name="7714-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1487,19 +1487,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6F9DFAB-9FE7-4CAF-B2E7-F47F71AFFB78}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA854FC-3AB9-4785-8D43-886199B49177}">
   <dimension ref="A1:R12"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" customWidth="1"/>
-    <col min="3" max="13" width="7.44140625" customWidth="1"/>
-    <col min="14" max="14" width="7.77734375" customWidth="1"/>
-    <col min="15" max="17" width="7.44140625" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="15.125" customWidth="1"/>
+    <col min="3" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1527,7 +1527,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1557,7 +1557,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1653,7 +1653,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>1.72</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>2.77</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="41">
         <v>2024</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="43" t="s">
         <v>25</v>
       </c>
@@ -1985,7 +1985,7 @@
         <v>1.67</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="44"/>
       <c r="B11" s="22" t="s">
         <v>33</v>
@@ -2007,7 +2007,7 @@
       <c r="Q11" s="48"/>
       <c r="R11" s="48"/>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
         <v>35</v>
       </c>
